--- a/data/trans_orig/P46-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P46-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la opinión que tienen si tomasen el sol sin ninguna protección en 2007</t>
+          <t>Población según la opinión que tienen si tomasen el sol sin ninguna protección en 2007 (tasa de respuesta: 97,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12338</t>
+          <t>12657</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31003</t>
+          <t>30286</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>960</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15220</t>
+          <t>15448</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34349</t>
+          <t>35258</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46555</t>
+          <t>45463</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76835</t>
+          <t>75123</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17881</t>
+          <t>17340</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38943</t>
+          <t>37793</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70571</t>
+          <t>70317</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>106247</t>
+          <t>105760</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>97870</t>
+          <t>97663</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>135635</t>
+          <t>136026</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34140</t>
+          <t>33193</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60559</t>
+          <t>58781</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>141006</t>
+          <t>138828</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>184504</t>
+          <t>186665</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>249745</t>
+          <t>248533</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>298399</t>
+          <t>301188</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>249396</t>
+          <t>249142</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>299524</t>
+          <t>298487</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>509327</t>
+          <t>510598</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>582900</t>
+          <t>582735</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,92%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>112988</t>
+          <t>111519</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>153478</t>
+          <t>153199</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>196035</t>
+          <t>196071</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>243465</t>
+          <t>242367</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>320789</t>
+          <t>318126</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>383764</t>
+          <t>382485</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,17%</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58495</t>
+          <t>59295</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>92701</t>
+          <t>92584</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>98011</t>
+          <t>96913</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>134026</t>
+          <t>135111</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>163926</t>
+          <t>162662</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>216581</t>
+          <t>214246</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27803</t>
+          <t>26948</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53682</t>
+          <t>52743</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>9569</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26049</t>
+          <t>27009</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42340</t>
+          <t>41542</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74902</t>
+          <t>72333</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44035</t>
+          <t>44748</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>75838</t>
+          <t>75860</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17281</t>
+          <t>16294</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39661</t>
+          <t>38265</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>66243</t>
+          <t>65710</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>105869</t>
+          <t>104635</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>129369</t>
+          <t>128902</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>175553</t>
+          <t>175275</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41277</t>
+          <t>41081</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72514</t>
+          <t>73915</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>177597</t>
+          <t>180267</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>232200</t>
+          <t>234639</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>287432</t>
+          <t>285603</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>346487</t>
+          <t>347768</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>307278</t>
+          <t>302423</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>365640</t>
+          <t>368423</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>610330</t>
+          <t>610035</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>693252</t>
+          <t>700251</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,88%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>199058</t>
+          <t>197722</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>250983</t>
+          <t>253479</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>270183</t>
+          <t>267405</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>328295</t>
+          <t>328474</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>480767</t>
+          <t>482491</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>563154</t>
+          <t>566031</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,81%</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>133857</t>
+          <t>134847</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>180179</t>
+          <t>182839</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>195178</t>
+          <t>195652</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>248838</t>
+          <t>250063</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>345436</t>
+          <t>341879</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>418478</t>
+          <t>414285</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21589</t>
+          <t>21093</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10666</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9612</t>
+          <t>9894</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>28285</t>
+          <t>28062</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66486</t>
+          <t>66681</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>102172</t>
+          <t>102622</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31965</t>
+          <t>32431</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57889</t>
+          <t>57717</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>106625</t>
+          <t>107670</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>149373</t>
+          <t>151199</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95046</t>
+          <t>95851</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>135377</t>
+          <t>137055</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>44236</t>
+          <t>44025</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>72166</t>
+          <t>72302</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>149066</t>
+          <t>147948</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>197479</t>
+          <t>197915</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>192852</t>
+          <t>194044</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>245859</t>
+          <t>244393</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>192674</t>
+          <t>192526</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>242424</t>
+          <t>238119</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>402970</t>
+          <t>401337</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>469561</t>
+          <t>472239</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,49%</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>95426</t>
+          <t>93960</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>134857</t>
+          <t>134113</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>154486</t>
+          <t>156045</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>197580</t>
+          <t>198592</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>259888</t>
+          <t>260482</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>321307</t>
+          <t>319866</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,04%</t>
         </is>
       </c>
     </row>
@@ -2887,12 +2887,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>94075</t>
+          <t>94576</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>134900</t>
+          <t>134607</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>153442</t>
+          <t>153743</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>196965</t>
+          <t>195891</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>262050</t>
+          <t>258549</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>319811</t>
+          <t>317011</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12841</t>
+          <t>12785</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30647</t>
+          <t>31996</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20136</t>
+          <t>18699</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21210</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>45040</t>
+          <t>43913</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>35805</t>
+          <t>35605</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>62168</t>
+          <t>61600</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>25489</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>50100</t>
+          <t>50096</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>67650</t>
+          <t>68872</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>101729</t>
+          <t>103981</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>87997</t>
+          <t>87382</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>126186</t>
+          <t>126672</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>53429</t>
+          <t>53307</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>88421</t>
+          <t>85892</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>150727</t>
+          <t>153359</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>200678</t>
+          <t>206167</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -3456,12 +3456,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>286615</t>
+          <t>284502</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>341706</t>
+          <t>340251</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>282239</t>
+          <t>281762</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>341431</t>
+          <t>341972</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>583513</t>
+          <t>583433</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>663258</t>
+          <t>667417</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,04%</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>214351</t>
+          <t>213447</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>264536</t>
+          <t>264247</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>276185</t>
+          <t>277270</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>333628</t>
+          <t>335892</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>504245</t>
+          <t>501866</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>582367</t>
+          <t>583508</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -3682,12 +3682,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>150738</t>
+          <t>150421</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>196775</t>
+          <t>194288</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3697,12 +3697,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>247976</t>
+          <t>248105</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>305739</t>
+          <t>304094</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>412962</t>
+          <t>411443</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>487005</t>
+          <t>484419</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>75181</t>
+          <t>73122</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>113870</t>
+          <t>111827</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>24924</t>
+          <t>23893</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>50493</t>
+          <t>48570</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>106978</t>
+          <t>104315</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>151387</t>
+          <t>151094</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4025,12 +4025,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>221938</t>
+          <t>219907</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>283652</t>
+          <t>283488</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -4060,12 +4060,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>110681</t>
+          <t>112099</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>157732</t>
+          <t>157954</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>346365</t>
+          <t>344247</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>418143</t>
+          <t>421936</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4110,12 +4110,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>448452</t>
+          <t>443392</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>533610</t>
+          <t>526992</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>195611</t>
+          <t>197043</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>257398</t>
+          <t>257335</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>666790</t>
+          <t>665950</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>765628</t>
+          <t>769904</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4223,12 +4223,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -4251,12 +4251,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1068094</t>
+          <t>1067727</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1177880</t>
+          <t>1176198</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4266,12 +4266,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1082666</t>
+          <t>1084373</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1191139</t>
+          <t>1195445</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2182093</t>
+          <t>2181801</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2337264</t>
+          <t>2332734</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -4364,12 +4364,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>663014</t>
+          <t>665386</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>756519</t>
+          <t>754686</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>944716</t>
+          <t>943274</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1047075</t>
+          <t>1049437</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1636431</t>
+          <t>1638504</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1776460</t>
+          <t>1790945</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,59%</t>
         </is>
       </c>
     </row>
@@ -4477,12 +4477,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>477751</t>
+          <t>479518</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>561197</t>
+          <t>562080</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4492,12 +4492,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>744355</t>
+          <t>742461</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>843269</t>
+          <t>841927</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1234904</t>
+          <t>1241573</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1367968</t>
+          <t>1369430</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la opinión que tienen si tomasen el sol sin ninguna protección en 2012</t>
+          <t>Población según la opinión que tienen si tomasen el sol sin ninguna protección en 2012 (tasa de respuesta: 98,05%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45973</t>
+          <t>45934</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75418</t>
+          <t>76878</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29239</t>
+          <t>28296</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53472</t>
+          <t>53744</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80880</t>
+          <t>81032</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>120354</t>
+          <t>120112</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68165</t>
+          <t>68175</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103956</t>
+          <t>104158</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41383</t>
+          <t>42578</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69706</t>
+          <t>70179</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117890</t>
+          <t>118001</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>165279</t>
+          <t>166650</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83532</t>
+          <t>84826</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>122437</t>
+          <t>122806</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49822</t>
+          <t>49781</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>83352</t>
+          <t>82763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>145204</t>
+          <t>145928</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>192792</t>
+          <t>196438</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>167365</t>
+          <t>165617</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>212736</t>
+          <t>214409</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>141682</t>
+          <t>142379</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>189489</t>
+          <t>188879</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>322421</t>
+          <t>318207</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>387270</t>
+          <t>384995</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>129126</t>
+          <t>130773</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>175184</t>
+          <t>175265</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>189941</t>
+          <t>190130</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>240694</t>
+          <t>240025</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>332450</t>
+          <t>332167</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>396709</t>
+          <t>397755</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,97%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91539</t>
+          <t>90363</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>130851</t>
+          <t>131039</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>119942</t>
+          <t>120419</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>163552</t>
+          <t>162802</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>223106</t>
+          <t>220507</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>281619</t>
+          <t>281606</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -5734,12 +5734,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37740</t>
+          <t>35519</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67972</t>
+          <t>64656</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19018</t>
+          <t>19354</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41836</t>
+          <t>41938</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60472</t>
+          <t>63532</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>97883</t>
+          <t>100281</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -5847,12 +5847,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>102379</t>
+          <t>104677</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>149315</t>
+          <t>149566</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62646</t>
+          <t>60958</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>98964</t>
+          <t>94599</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>174351</t>
+          <t>175768</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>230981</t>
+          <t>234460</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -5960,12 +5960,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>150701</t>
+          <t>150886</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>200201</t>
+          <t>200899</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86189</t>
+          <t>84795</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>128792</t>
+          <t>125979</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>246398</t>
+          <t>246742</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>315253</t>
+          <t>312203</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,61%</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>230194</t>
+          <t>227912</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>287593</t>
+          <t>287436</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>187143</t>
+          <t>186063</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>242600</t>
+          <t>239842</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>430338</t>
+          <t>427881</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>507917</t>
+          <t>506680</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,34%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>167194</t>
+          <t>168997</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>219251</t>
+          <t>220866</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>215936</t>
+          <t>215304</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>272198</t>
+          <t>271566</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>399148</t>
+          <t>400212</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>475074</t>
+          <t>478001</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>182972</t>
+          <t>180760</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>234143</t>
+          <t>233131</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>295287</t>
+          <t>299123</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>355878</t>
+          <t>358987</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>494313</t>
+          <t>493496</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>576583</t>
+          <t>573383</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,68%</t>
         </is>
       </c>
     </row>
@@ -6529,12 +6529,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19667</t>
+          <t>19289</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41092</t>
+          <t>40387</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2359</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13259</t>
+          <t>13958</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25004</t>
+          <t>24440</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49388</t>
+          <t>47283</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -6642,12 +6642,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55590</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>89489</t>
+          <t>90050</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39931</t>
+          <t>39855</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68993</t>
+          <t>69925</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>104902</t>
+          <t>103835</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>149515</t>
+          <t>149370</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>99736</t>
+          <t>97295</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>144607</t>
+          <t>138444</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51921</t>
+          <t>50107</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>84718</t>
+          <t>84239</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>158383</t>
+          <t>156633</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>212393</t>
+          <t>211100</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>157050</t>
+          <t>156451</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>206254</t>
+          <t>205620</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>139332</t>
+          <t>141807</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>188725</t>
+          <t>189347</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>313059</t>
+          <t>309249</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>379662</t>
+          <t>380391</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>120765</t>
+          <t>120856</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>166787</t>
+          <t>167678</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>174304</t>
+          <t>173332</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>224032</t>
+          <t>226749</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>310591</t>
+          <t>307959</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>383258</t>
+          <t>374811</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>174614</t>
+          <t>177504</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>226306</t>
+          <t>229174</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>245502</t>
+          <t>245704</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>301795</t>
+          <t>300258</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>436791</t>
+          <t>438623</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>513287</t>
+          <t>515845</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -7324,12 +7324,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24888</t>
+          <t>25135</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51976</t>
+          <t>51071</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7339,12 +7339,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21339</t>
+          <t>20661</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43171</t>
+          <t>42497</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>51547</t>
+          <t>51773</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>85917</t>
+          <t>83650</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -7437,12 +7437,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>108341</t>
+          <t>109134</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>151357</t>
+          <t>152318</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7452,12 +7452,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7472,12 +7472,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>78679</t>
+          <t>76454</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>118217</t>
+          <t>115738</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>198359</t>
+          <t>198035</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>257571</t>
+          <t>257513</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -7550,12 +7550,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>120772</t>
+          <t>121686</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>166409</t>
+          <t>165354</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7565,12 +7565,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7585,12 +7585,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>116689</t>
+          <t>117123</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>160317</t>
+          <t>161342</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>249560</t>
+          <t>248776</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>315305</t>
+          <t>312409</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -7663,12 +7663,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>269394</t>
+          <t>270466</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>328854</t>
+          <t>329678</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7678,12 +7678,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7698,12 +7698,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>258086</t>
+          <t>256105</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>317249</t>
+          <t>314697</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>544729</t>
+          <t>540994</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>623877</t>
+          <t>624900</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>179179</t>
+          <t>179648</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>232586</t>
+          <t>229841</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7811,12 +7811,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>256488</t>
+          <t>257294</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>313730</t>
+          <t>318258</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>455030</t>
+          <t>452000</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>533388</t>
+          <t>528634</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,9%</t>
         </is>
       </c>
     </row>
@@ -7889,12 +7889,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>102205</t>
+          <t>103069</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>145667</t>
+          <t>145222</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>173819</t>
+          <t>171818</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>226246</t>
+          <t>222280</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>286431</t>
+          <t>287395</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>354593</t>
+          <t>354904</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7974,12 +7974,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -8119,12 +8119,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>149850</t>
+          <t>148629</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>203005</t>
+          <t>205983</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8154,12 +8154,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>84892</t>
+          <t>86380</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>127932</t>
+          <t>127172</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>247116</t>
+          <t>246301</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>314818</t>
+          <t>316036</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -8232,12 +8232,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>370644</t>
+          <t>371935</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>450581</t>
+          <t>449088</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8267,12 +8267,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>248662</t>
+          <t>250301</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>318496</t>
+          <t>316401</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>639236</t>
+          <t>644649</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>746419</t>
+          <t>753897</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -8345,12 +8345,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>493495</t>
+          <t>494036</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>577572</t>
+          <t>581836</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8360,12 +8360,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8380,12 +8380,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>340188</t>
+          <t>338355</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>415629</t>
+          <t>414980</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8395,12 +8395,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8415,12 +8415,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>853823</t>
+          <t>856734</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>970588</t>
+          <t>970418</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>868828</t>
+          <t>871343</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>975537</t>
+          <t>972155</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8473,12 +8473,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>776468</t>
+          <t>772759</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>880697</t>
+          <t>878540</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8508,12 +8508,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8528,12 +8528,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1675917</t>
+          <t>1675959</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1823860</t>
+          <t>1824504</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -8571,12 +8571,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>641220</t>
+          <t>644957</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>739698</t>
+          <t>740145</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8586,12 +8586,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>887206</t>
+          <t>888116</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>995261</t>
+          <t>995603</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8621,12 +8621,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1559926</t>
+          <t>1563919</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1703339</t>
+          <t>1709255</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8656,12 +8656,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -8684,12 +8684,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>596170</t>
+          <t>594126</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>694867</t>
+          <t>691816</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8699,12 +8699,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8719,12 +8719,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>879709</t>
+          <t>881024</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>991012</t>
+          <t>990308</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1505721</t>
+          <t>1506615</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1651012</t>
+          <t>1649777</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,09%</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la opinión que tienen si tomasen el sol sin ninguna protección en 2016</t>
+          <t>Población según la opinión que tienen si tomasen el sol sin ninguna protección en 2016 (tasa de respuesta: 99,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9146,12 +9146,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31957</t>
+          <t>31895</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57101</t>
+          <t>59962</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9181,12 +9181,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8145</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22994</t>
+          <t>23243</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45375</t>
+          <t>44631</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75805</t>
+          <t>76212</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -9259,12 +9259,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63812</t>
+          <t>62424</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96017</t>
+          <t>97921</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35438</t>
+          <t>35016</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62127</t>
+          <t>62437</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106577</t>
+          <t>105714</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150395</t>
+          <t>149173</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -9372,12 +9372,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>135273</t>
+          <t>130715</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>175528</t>
+          <t>176193</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9387,12 +9387,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>68764</t>
+          <t>68909</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>102279</t>
+          <t>100969</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>210639</t>
+          <t>211783</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>268383</t>
+          <t>265522</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,05%</t>
         </is>
       </c>
     </row>
@@ -9485,12 +9485,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>160062</t>
+          <t>158883</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>204963</t>
+          <t>203959</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9500,12 +9500,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>180808</t>
+          <t>181799</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>229049</t>
+          <t>228746</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9535,12 +9535,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>351411</t>
+          <t>352874</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>416774</t>
+          <t>416472</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9570,12 +9570,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,44%</t>
         </is>
       </c>
     </row>
@@ -9598,12 +9598,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>103956</t>
+          <t>104342</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>143147</t>
+          <t>143119</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>147261</t>
+          <t>146330</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>191965</t>
+          <t>193258</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9648,12 +9648,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>264684</t>
+          <t>261257</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>324569</t>
+          <t>322433</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9683,12 +9683,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,34%</t>
         </is>
       </c>
     </row>
@@ -9711,12 +9711,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63317</t>
+          <t>64599</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>98830</t>
+          <t>100158</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9726,12 +9726,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>121491</t>
+          <t>122856</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>164572</t>
+          <t>165503</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9761,12 +9761,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>197022</t>
+          <t>196863</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>252715</t>
+          <t>252909</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -9941,12 +9941,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28470</t>
+          <t>28036</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53415</t>
+          <t>52617</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9956,12 +9956,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29818</t>
+          <t>29969</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9991,12 +9991,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44749</t>
+          <t>44262</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74603</t>
+          <t>74913</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10026,12 +10026,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -10054,12 +10054,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59980</t>
+          <t>59934</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>95647</t>
+          <t>92642</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41752</t>
+          <t>41979</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74089</t>
+          <t>72499</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10104,12 +10104,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>110545</t>
+          <t>108838</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>152995</t>
+          <t>153100</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -10167,12 +10167,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>176894</t>
+          <t>175796</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>228256</t>
+          <t>225750</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10182,12 +10182,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76999</t>
+          <t>76229</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114538</t>
+          <t>113368</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10217,12 +10217,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>263393</t>
+          <t>264626</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>330670</t>
+          <t>331969</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10252,12 +10252,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -10280,12 +10280,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>308319</t>
+          <t>309066</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>369420</t>
+          <t>369418</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>316910</t>
+          <t>319768</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>381270</t>
+          <t>381618</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10330,12 +10330,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>650083</t>
+          <t>645546</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>738435</t>
+          <t>735853</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10365,12 +10365,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,92%</t>
         </is>
       </c>
     </row>
@@ -10393,12 +10393,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>170649</t>
+          <t>172941</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>225589</t>
+          <t>224053</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10428,12 +10428,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>264353</t>
+          <t>264792</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>325780</t>
+          <t>319677</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10443,12 +10443,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10463,12 +10463,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>450630</t>
+          <t>453388</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>530789</t>
+          <t>532484</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10478,12 +10478,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -10506,12 +10506,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>132678</t>
+          <t>133002</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>179378</t>
+          <t>178312</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10541,12 +10541,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>200103</t>
+          <t>199863</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>255955</t>
+          <t>255046</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10556,12 +10556,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>344791</t>
+          <t>346757</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>420619</t>
+          <t>417355</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10591,12 +10591,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -10736,12 +10736,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17134</t>
+          <t>16834</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38922</t>
+          <t>38763</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10751,12 +10751,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10771,12 +10771,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22987</t>
+          <t>21992</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10786,12 +10786,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10806,12 +10806,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28822</t>
+          <t>28226</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>54182</t>
+          <t>54561</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10821,12 +10821,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -10849,12 +10849,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74419</t>
+          <t>74042</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>112313</t>
+          <t>115131</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10884,12 +10884,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39091</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67230</t>
+          <t>65810</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10899,12 +10899,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10919,12 +10919,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>122471</t>
+          <t>122581</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>169442</t>
+          <t>168573</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10934,12 +10934,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -10962,12 +10962,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95382</t>
+          <t>94719</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>137586</t>
+          <t>137092</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10997,12 +10997,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>75909</t>
+          <t>77976</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>113474</t>
+          <t>115862</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11012,12 +11012,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11032,12 +11032,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>182928</t>
+          <t>182869</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>237953</t>
+          <t>237623</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11047,12 +11047,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -11075,12 +11075,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>192353</t>
+          <t>195470</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>243170</t>
+          <t>244750</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11110,12 +11110,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>181926</t>
+          <t>181879</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>232392</t>
+          <t>232024</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11145,12 +11145,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>386046</t>
+          <t>388485</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>455655</t>
+          <t>459009</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11160,12 +11160,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,95%</t>
         </is>
       </c>
     </row>
@@ -11188,12 +11188,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>126124</t>
+          <t>126291</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>173114</t>
+          <t>168753</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11223,12 +11223,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>195182</t>
+          <t>193959</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>246171</t>
+          <t>247595</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11258,12 +11258,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>337331</t>
+          <t>337447</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>405681</t>
+          <t>406346</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11273,12 +11273,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -11301,12 +11301,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>128666</t>
+          <t>130312</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>175644</t>
+          <t>175159</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11316,12 +11316,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11336,12 +11336,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>171444</t>
+          <t>169575</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>221509</t>
+          <t>220484</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11371,12 +11371,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>315087</t>
+          <t>315000</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>379628</t>
+          <t>385049</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -11531,12 +11531,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39940</t>
+          <t>39031</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>68886</t>
+          <t>68592</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11566,12 +11566,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20244</t>
+          <t>19829</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>42014</t>
+          <t>42309</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11601,12 +11601,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>66427</t>
+          <t>67436</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>104720</t>
+          <t>103979</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11616,12 +11616,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -11644,12 +11644,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>54057</t>
+          <t>53495</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>88725</t>
+          <t>87522</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11659,12 +11659,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11679,12 +11679,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29514</t>
+          <t>28517</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>54650</t>
+          <t>55886</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11714,12 +11714,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>90497</t>
+          <t>90271</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>130925</t>
+          <t>134533</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -11757,12 +11757,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>119584</t>
+          <t>118691</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>162834</t>
+          <t>162003</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11772,12 +11772,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11792,12 +11792,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>72959</t>
+          <t>72208</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>110866</t>
+          <t>109482</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11827,12 +11827,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>201257</t>
+          <t>203699</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>260320</t>
+          <t>260874</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -11870,12 +11870,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>270840</t>
+          <t>269328</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>325638</t>
+          <t>325282</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11905,12 +11905,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>306349</t>
+          <t>309378</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>369375</t>
+          <t>369318</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11940,12 +11940,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>596390</t>
+          <t>591014</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>677280</t>
+          <t>676441</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,45%</t>
         </is>
       </c>
     </row>
@@ -11983,12 +11983,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>193196</t>
+          <t>192471</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>245514</t>
+          <t>244941</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11998,12 +11998,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12018,12 +12018,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>250223</t>
+          <t>256719</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>311436</t>
+          <t>310594</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12053,12 +12053,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>465840</t>
+          <t>464289</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>540756</t>
+          <t>540447</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,53%</t>
         </is>
       </c>
     </row>
@@ -12096,12 +12096,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>125671</t>
+          <t>125028</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>173047</t>
+          <t>170857</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12111,12 +12111,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12131,12 +12131,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>228959</t>
+          <t>230902</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>286932</t>
+          <t>288868</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12166,12 +12166,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>369632</t>
+          <t>367976</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>442942</t>
+          <t>441019</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -12326,12 +12326,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>141002</t>
+          <t>139482</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>190408</t>
+          <t>190029</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12341,12 +12341,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12361,12 +12361,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>61361</t>
+          <t>62561</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>99277</t>
+          <t>96721</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>210055</t>
+          <t>210830</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>272837</t>
+          <t>273930</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -12439,12 +12439,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>280528</t>
+          <t>284049</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>353558</t>
+          <t>351389</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12454,12 +12454,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12474,12 +12474,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>167486</t>
+          <t>166108</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>224795</t>
+          <t>220890</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12509,12 +12509,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>470909</t>
+          <t>468862</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>558366</t>
+          <t>556236</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -12552,12 +12552,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>563517</t>
+          <t>567003</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>658854</t>
+          <t>659104</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12567,12 +12567,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12587,12 +12587,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>328599</t>
+          <t>326385</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>400736</t>
+          <t>403590</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12622,12 +12622,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>915087</t>
+          <t>919267</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1030927</t>
+          <t>1036130</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>984440</t>
+          <t>981674</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1094390</t>
+          <t>1090915</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12680,12 +12680,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12700,12 +12700,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1045309</t>
+          <t>1045021</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1151421</t>
+          <t>1152688</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12735,12 +12735,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2060667</t>
+          <t>2047695</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2219410</t>
+          <t>2208829</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -12778,12 +12778,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>643545</t>
+          <t>642595</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>738860</t>
+          <t>739191</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12793,12 +12793,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12813,12 +12813,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>911362</t>
+          <t>911814</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1017247</t>
+          <t>1018130</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12848,12 +12848,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1580538</t>
+          <t>1580429</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1722071</t>
+          <t>1726331</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -12891,12 +12891,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>496667</t>
+          <t>491852</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>583391</t>
+          <t>581347</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12906,12 +12906,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12926,12 +12926,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>769865</t>
+          <t>763507</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>871182</t>
+          <t>869276</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12941,12 +12941,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12961,12 +12961,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1295098</t>
+          <t>1286308</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1427411</t>
+          <t>1426748</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -12976,12 +12976,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
